--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N162_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N162_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.23092831699602</v>
+        <v>7.350025851511854</v>
       </c>
       <c r="D2" t="n">
-        <v>43.01757160441223</v>
+        <v>6.990355385716986</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F2" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.605922527730506</v>
+        <v>0.4234624107562072</v>
       </c>
       <c r="D3" t="n">
-        <v>6.104648608934066</v>
+        <v>0.9920053989517857</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F3" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.47299626566859</v>
+        <v>2.351861893171145</v>
       </c>
       <c r="D4" t="n">
-        <v>15.95731533563063</v>
+        <v>2.593063742039977</v>
       </c>
       <c r="E4" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F4" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.67617123357781</v>
+        <v>3.847377825456395</v>
       </c>
       <c r="D5" t="n">
-        <v>24.20611444750567</v>
+        <v>3.933493597719672</v>
       </c>
       <c r="E5" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F5" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.16640805551707</v>
+        <v>6.202041309021525</v>
       </c>
       <c r="D6" t="n">
-        <v>38.99989789735519</v>
+        <v>6.337483408320218</v>
       </c>
       <c r="E6" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F6" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.830811612996705</v>
+        <v>0.7850068871119645</v>
       </c>
       <c r="D7" t="n">
-        <v>15.8730368365491</v>
+        <v>2.579368485939229</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F7" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.81220325696309</v>
+        <v>5.169483029256503</v>
       </c>
       <c r="D8" t="n">
-        <v>32.01072262347769</v>
+        <v>5.201742426315125</v>
       </c>
       <c r="E8" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F8" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>6.553936703823335</v>
+        <v>1.065014714371292</v>
       </c>
       <c r="D9" t="n">
-        <v>9.02426206603471</v>
+        <v>1.46644258573064</v>
       </c>
       <c r="E9" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F9" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.66586059392653</v>
+        <v>3.033202346513062</v>
       </c>
       <c r="D10" t="n">
-        <v>19.49372820005745</v>
+        <v>3.167730832509335</v>
       </c>
       <c r="E10" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F10" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.6345047660921</v>
+        <v>5.953107024489967</v>
       </c>
       <c r="D11" t="n">
-        <v>34.90944367553143</v>
+        <v>5.672784597273858</v>
       </c>
       <c r="E11" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F11" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>5.830951894845301</v>
+        <v>0.9475296829123614</v>
       </c>
       <c r="D12" t="n">
-        <v>6.503254522668519</v>
+        <v>1.056778859933635</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F12" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.91600690310462</v>
+        <v>3.398851121754501</v>
       </c>
       <c r="D13" t="n">
-        <v>22.01187918859239</v>
+        <v>3.576930368146264</v>
       </c>
       <c r="E13" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F13" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.63904493628429</v>
+        <v>7.091344802146197</v>
       </c>
       <c r="D14" t="n">
-        <v>7.333509994962336</v>
+        <v>1.19169537418138</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F14" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.22458371518492</v>
+        <v>4.911494853717549</v>
       </c>
       <c r="D15" t="n">
-        <v>30.63341921086247</v>
+        <v>4.977930621765151</v>
       </c>
       <c r="E15" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F15" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.00724307865413</v>
+        <v>4.551177000281297</v>
       </c>
       <c r="D16" t="n">
-        <v>24.05202694161139</v>
+        <v>3.908454378011851</v>
       </c>
       <c r="E16" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F16" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>28.00677556789221</v>
+        <v>4.551101029782483</v>
       </c>
       <c r="D17" t="n">
-        <v>21.66088370643233</v>
+        <v>3.519893602295254</v>
       </c>
       <c r="E17" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F17" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>27.61528832084549</v>
+        <v>4.487484352137392</v>
       </c>
       <c r="D18" t="n">
-        <v>27.59092212466647</v>
+        <v>4.483524845258303</v>
       </c>
       <c r="E18" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F18" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.57795025724906</v>
+        <v>6.268916916802973</v>
       </c>
       <c r="D19" t="n">
-        <v>16.01200854915488</v>
+        <v>2.601951389237668</v>
       </c>
       <c r="E19" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F19" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>32.008313003228</v>
+        <v>5.201350863024549</v>
       </c>
       <c r="D20" t="n">
-        <v>16.77050983124842</v>
+        <v>2.725207847577868</v>
       </c>
       <c r="E20" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F20" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>25.02846970296256</v>
+        <v>4.067126326731416</v>
       </c>
       <c r="D21" t="n">
-        <v>24.84293247331887</v>
+        <v>4.036976526914316</v>
       </c>
       <c r="E21" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F21" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>24.4443564686256</v>
+        <v>3.97220792615166</v>
       </c>
       <c r="D22" t="n">
-        <v>24.10407199299683</v>
+        <v>3.916911698861985</v>
       </c>
       <c r="E22" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F22" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>33.72152421961326</v>
+        <v>5.479747685687156</v>
       </c>
       <c r="D23" t="n">
-        <v>9.656603957913983</v>
+        <v>1.569198143161022</v>
       </c>
       <c r="E23" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F23" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>28.63331426660285</v>
+        <v>4.652913568322963</v>
       </c>
       <c r="D24" t="n">
-        <v>9.656603957913983</v>
+        <v>1.569198143161022</v>
       </c>
       <c r="E24" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F24" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>35.88524808879316</v>
+        <v>5.831352814428889</v>
       </c>
       <c r="D25" t="n">
-        <v>19.94962299591864</v>
+        <v>3.241813736836779</v>
       </c>
       <c r="E25" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F25" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>17.19159457152274</v>
+        <v>2.793634117872445</v>
       </c>
       <c r="D26" t="n">
-        <v>16.77912081544281</v>
+        <v>2.726607132509457</v>
       </c>
       <c r="E26" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F26" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>19.46132178302827</v>
+        <v>3.162464789742093</v>
       </c>
       <c r="D27" t="n">
-        <v>19.27504926327734</v>
+        <v>3.132195505282568</v>
       </c>
       <c r="E27" t="n">
-        <v>11.5645580987879</v>
+        <v>1.879240691053035</v>
       </c>
       <c r="F27" t="n">
-        <v>9.687157538375295</v>
+        <v>1.574163099985986</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
